--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5405.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5405.xlsx
@@ -2323,12 +2323,18 @@
           <t>5405-16-24</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>2.46</v>
+      </c>
       <c r="C34" t="n">
         <v>2.375</v>
       </c>
       <c r="D34" t="n">
         <v>0.9379999999999999</v>
       </c>
+      <c r="E34" t="n">
+        <v>1.72</v>
+      </c>
       <c r="F34" t="n">
         <v>1.315</v>
       </c>
@@ -2342,17 +2348,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: CHEX@HEX, D@BORE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: CHEX@HEX, D@BORE, L@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5405-16-24 (PARTcommunity / CADENAS, CHEX@HEX=C, D@BORE=A1D, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5405-16-24 (PARTcommunity / CADENAS, CHEX@HEX=C, D@BORE=A1D, L@DRIVE=L, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2442,12 +2448,18 @@
           <t>5405-20-32</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>2.6</v>
+      </c>
       <c r="C36" t="n">
         <v>2.875</v>
       </c>
       <c r="D36" t="n">
         <v>1.25</v>
       </c>
+      <c r="E36" t="n">
+        <v>2.2</v>
+      </c>
       <c r="F36" t="n">
         <v>1.66</v>
       </c>
@@ -2466,12 +2478,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: CHEX@HEX, D@BORE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: CHEX@HEX, D@BORE, L@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5405-20-32 (PARTcommunity / CADENAS, CHEX@HEX=C, D@BORE=A1D, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5405-20-32 (PARTcommunity / CADENAS, CHEX@HEX=C, D@BORE=A1D, L@DRIVE=L, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5405.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5405.xlsx
@@ -2473,7 +2473,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
